--- a/output/pdf_financials_xlsx/BARK.xlsx
+++ b/output/pdf_financials_xlsx/BARK.xlsx
@@ -5320,43 +5320,43 @@
         <v>0.152252</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.152252</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.303099</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.303099</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.303099</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.303099</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.303099</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.303099</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.303099</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.303099</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.303499</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.554563</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.693151</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.359194</v>
       </c>
     </row>
     <row r="93">
@@ -6657,13 +6657,13 @@
         <v>-0.7</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.552964</v>
+        <v>-0.9819020000000001</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>2.106199</v>
+        <v>1.324731</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>2.919681</v>
+        <v>0.845672</v>
       </c>
     </row>
     <row r="119">
@@ -9325,7 +9325,11 @@
           <t>Share-based payment reserve 8,10,11</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10482,7 +10486,11 @@
           <t>Share-based payment reserve 5,6,7</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -11396,7 +11404,11 @@
           <t>Share-based payment reserve 6,7</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -13872,7 +13884,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -18113,7 +18129,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -19802,7 +19822,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BARK.xlsx
+++ b/output/pdf_financials_xlsx/BARK.xlsx
@@ -884,46 +884,46 @@
         <v>0.000204</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.028062</v>
+        <v>0.191188</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.01517</v>
+        <v>0.037469</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.056048</v>
+        <v>0.369722</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.07223499999999999</v>
+        <v>0.659982</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.100081</v>
+        <v>0.818514</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.095966</v>
+        <v>0.695491</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.09762999999999999</v>
+        <v>0.181719</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.0925</v>
+        <v>0.150274</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.047</v>
+        <v>0.081728</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.003</v>
+        <v>0.218336</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.21</v>
+        <v>0.232062</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.120928</v>
+        <v>0.521601</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.495137</v>
+        <v>2.27596</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.346588</v>
+        <v>1.376549</v>
       </c>
     </row>
     <row r="11">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.455712</v>
+        <v>0.142038</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.143407</v>
+        <v>0.55566</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.595195</v>
+        <v>-0.123238</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.142471</v>
+        <v>-0.457054</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.077377</v>
+        <v>-0.161466</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.047</v>
+        <v>-0.081728</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.003</v>
+        <v>-0.218336</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.232062</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.120928</v>
+        <v>-0.521601</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.495137</v>
+        <v>-2.27596</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.346588</v>
+        <v>-1.376549</v>
       </c>
     </row>
     <row r="12">
@@ -996,46 +996,46 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004793</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.008560999999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004602</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.006085</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006258</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.005172</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.007711</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.011979</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.018441</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.010916</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000315</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.007957000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1850,46 +1850,46 @@
         <v>-0.055244</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.186395</v>
+        <v>-0.191188</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.028908</v>
+        <v>-0.037469</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.117868</v>
+        <v>0.113266</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.464958</v>
+        <v>0.458873</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.166972</v>
+        <v>-0.17323</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.540443</v>
+        <v>-0.545615</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.153755</v>
+        <v>-0.161466</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.138295</v>
+        <v>-0.150274</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.069728</v>
+        <v>-0.081728</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.199895</v>
+        <v>-0.218336</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.221146</v>
+        <v>-0.232062</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.530386</v>
+        <v>-0.530426</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.406822</v>
+        <v>-4.407137</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.82443</v>
+        <v>-3.832387</v>
       </c>
     </row>
     <row r="28">
@@ -1954,46 +1954,46 @@
         <v>-0.055244</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.186395</v>
+        <v>-0.191188</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.028908</v>
+        <v>-0.037469</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.117868</v>
+        <v>0.113266</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.464958</v>
+        <v>0.458873</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.166972</v>
+        <v>-0.17323</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.540443</v>
+        <v>-0.545615</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.153755</v>
+        <v>-0.161466</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.138295</v>
+        <v>-0.150274</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.069728</v>
+        <v>-0.081728</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.199895</v>
+        <v>-0.218336</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.221146</v>
+        <v>-0.232062</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.530386</v>
+        <v>-0.530426</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.406822</v>
+        <v>-4.407137</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.78661</v>
+        <v>-3.794567</v>
       </c>
     </row>
     <row r="30">
@@ -2018,19 +2018,19 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>23.03188994841332</v>
+        <v>22.13264030014069</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>38.2479381265208</v>
+        <v>37.74737957392061</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-24.01521122547017</v>
+        <v>-24.91528544060201</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-226.6607112151218</v>
+        <v>-228.8298376510357</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-759.1714807682813</v>
+        <v>-797.2448526144275</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2230,25 +2230,25 @@
         <v>0.668743</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.968327</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.906164</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.691446</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.345533</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000336</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.049444</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.239902</v>
       </c>
     </row>
     <row r="35">
@@ -2334,25 +2334,25 @@
         <v>0.668743</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.968327</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.906164</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.691446</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.345533</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000336</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.049444</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.239902</v>
       </c>
     </row>
     <row r="37">
@@ -2964,19 +2964,19 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.725196</v>
+        <v>0.03375</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.348918</v>
+        <v>0.003385</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.006157</v>
+        <v>0.005821</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.072675</v>
+        <v>0.023231</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.279738</v>
+        <v>0.039836</v>
       </c>
     </row>
     <row r="49">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -27837,7 +27837,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -27879,13 +27879,13 @@
         <v>0.232062</v>
       </c>
       <c r="Q226" s="5" t="n">
-        <v>-0.521601</v>
+        <v>0.521601</v>
       </c>
       <c r="R226" s="5" t="n">
-        <v>-2.27596</v>
+        <v>2.27596</v>
       </c>
       <c r="S226" s="5" t="n">
-        <v>-1.376549</v>
+        <v>1.376549</v>
       </c>
     </row>
     <row r="227">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -31071,7 +31071,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -35444,7 +35444,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -37909,7 +37909,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -38645,7 +38645,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -39290,7 +39290,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">

--- a/output/pdf_financials_xlsx/BARK.xlsx
+++ b/output/pdf_financials_xlsx/BARK.xlsx
@@ -761,13 +761,13 @@
         <v>0.21</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.120928</v>
+        <v>0.240928</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.495137</v>
+        <v>0.611556</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.346588</v>
+        <v>0.561488</v>
       </c>
     </row>
     <row r="8">
@@ -1268,10 +1268,10 @@
         <v>0.028278</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.001301</v>
+        <v>-0.025666</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.029579</v>
+        <v>-0.06773</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -2090,10 +2090,10 @@
         <v>6.081839650032906</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.7791725558776321</v>
+        <v>-15.37143952279424</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-5.473102621368025</v>
+        <v>-12.53231145560216</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -5743,37 +5743,37 @@
         <v>-0.004793</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.003498</v>
+        <v>-0.004048</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.260291</v>
+        <v>-0.293743</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.036029</v>
+        <v>0.073529</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.196167</v>
+        <v>0.19353</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.020311</v>
+        <v>0.018666</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.007784</v>
+        <v>0.007616</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000532</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000624</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00822</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.009651</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.043238</v>
       </c>
       <c r="O101" s="3" t="n">
         <v>-0.001307</v>
@@ -6003,37 +6003,37 @@
         <v>-0.096792</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.00321</v>
+        <v>0.00266</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.196133</v>
+        <v>-0.229585</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.004815</v>
+        <v>0.032685</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.213457</v>
+        <v>0.21082</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.006259</v>
+        <v>0.004614</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.002267</v>
+        <v>0.002099</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.000391</v>
+        <v>-0.000141</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.020189</v>
+        <v>0.019565</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.007887</v>
+        <v>-0.016107</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.010664</v>
+        <v>-0.001013</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.444693</v>
+        <v>0.401455</v>
       </c>
       <c r="O106" s="3" t="n">
         <v>0.107036</v>
@@ -6244,10 +6244,10 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.024978</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.028923</v>
       </c>
     </row>
     <row r="111">
@@ -17405,7 +17405,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -20653,7 +20657,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -21395,7 +21403,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -22065,7 +22077,11 @@
           <t>Proceeds from share issued</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -23236,7 +23252,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -24452,7 +24472,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -25081,7 +25105,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -27301,7 +27329,11 @@
           <t>Management and directors’ fees 12</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -30612,7 +30644,11 @@
           <t>Management and directors’ fees 8</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -34730,7 +34766,11 @@
           <t>Current income tax recovery</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -34819,7 +34859,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -36621,7 +36665,11 @@
           <t>Current income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -36710,7 +36758,11 @@
           <t>Total income tax recovery (expense) (Note 14)</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
